--- a/data/base/Backlog_12.xlsx
+++ b/data/base/Backlog_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D89DEE-136E-4447-B9DC-F04DFAF28BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66BB8998-1D1E-4B78-8411-4EFBE3B2341F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
+    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="34">
   <si>
     <t>Status</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>Mara neves</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -693,7 +696,7 @@
         <v>46111</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>15</v>
@@ -728,7 +731,7 @@
         <v>46111</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>15</v>
@@ -798,7 +801,7 @@
         <v>46111</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>15</v>
@@ -833,7 +836,7 @@
         <v>46111</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>15</v>
@@ -868,7 +871,7 @@
         <v>46111</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>15</v>
@@ -903,7 +906,7 @@
         <v>46111</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>15</v>
@@ -938,7 +941,7 @@
         <v>46111</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>15</v>
@@ -1008,7 +1011,7 @@
         <v>46111</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>15</v>
@@ -1113,7 +1116,7 @@
         <v>46111</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>15</v>
@@ -1253,7 +1256,7 @@
         <v>46111</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>15</v>
@@ -1288,7 +1291,7 @@
         <v>46111</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>15</v>
@@ -1358,7 +1361,7 @@
         <v>46111</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>15</v>
@@ -1598,7 +1601,7 @@
         <v>46111</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>2</v>
@@ -1633,7 +1636,7 @@
         <v>46111</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -1808,7 +1811,7 @@
         <v>46111</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>2</v>
@@ -1878,7 +1881,7 @@
         <v>46111</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>2</v>
@@ -1913,7 +1916,7 @@
         <v>46111</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>2</v>
@@ -1983,7 +1986,7 @@
         <v>46111</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>2</v>
@@ -2018,7 +2021,7 @@
         <v>46111</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>2</v>
